--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/4mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/15gps/4mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X32"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.55575391203</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>575.0328197884705</v>
       </c>
-      <c r="W2" t="b">
+      <c r="V2" t="b">
         <v>0</v>
       </c>
+      <c r="W2" t="s">
+        <v>29</v>
+      </c>
       <c r="X2">
-        <v>578.7331375234745</v>
+        <v>0.243786378</v>
+      </c>
+      <c r="Y2">
+        <v>0.261180772</v>
+      </c>
+      <c r="Z2">
+        <v>0.3572774744661001</v>
+      </c>
+      <c r="AA2">
+        <v>8.697197000000003</v>
+      </c>
+      <c r="AB2">
+        <v>0.04227924415535883</v>
+      </c>
+      <c r="AC2">
+        <v>24.3119529851812</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.55586965278</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>576.6040203409268</v>
       </c>
-      <c r="W3" t="b">
+      <c r="V3" t="b">
         <v>0</v>
       </c>
+      <c r="W3">
+        <v>578.4433571466049</v>
+      </c>
+      <c r="X3">
+        <v>0.243760666</v>
+      </c>
+      <c r="Y3">
+        <v>0.261185546</v>
+      </c>
+      <c r="Z3">
+        <v>0.357263420640963</v>
+      </c>
+      <c r="AA3">
+        <v>8.712440000000001</v>
+      </c>
+      <c r="AB3">
+        <v>0.04220784816869926</v>
+      </c>
+      <c r="AC3">
+        <v>24.33721494401142</v>
+      </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.55598597222</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>577.0320926704935</v>
       </c>
-      <c r="V4">
-        <v>1.052695678735621</v>
-      </c>
-      <c r="W4" t="b">
-        <v>1</v>
+      <c r="V4" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.243766698</v>
+      </c>
+      <c r="Y4">
+        <v>0.26118459</v>
+      </c>
+      <c r="Z4">
+        <v>0.3572668374020898</v>
+      </c>
+      <c r="AA4">
+        <v>8.708945999999997</v>
+      </c>
+      <c r="AB4">
+        <v>0.04222421263614579</v>
+      </c>
+      <c r="AC4">
+        <v>24.3647257787991</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.55610229167</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>573.8080643715872</v>
       </c>
-      <c r="V5">
-        <v>1.750950892799676</v>
-      </c>
-      <c r="W5" t="b">
-        <v>1</v>
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>24.35054470079342</v>
+      </c>
+      <c r="X5">
+        <v>0.243749556</v>
+      </c>
+      <c r="Y5">
+        <v>0.261176316</v>
+      </c>
+      <c r="Z5">
+        <v>0.3572490924964387</v>
+      </c>
+      <c r="AA5">
+        <v>8.713380000000001</v>
+      </c>
+      <c r="AB5">
+        <v>0.04220195283410719</v>
+      </c>
+      <c r="AC5">
+        <v>24.21582086844006</v>
       </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.55621803241</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>575.3894806745083</v>
       </c>
-      <c r="V6">
-        <v>1.612110943486277</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0.243747334</v>
+      </c>
+      <c r="Y6">
+        <v>0.261170586</v>
+      </c>
+      <c r="Z6">
+        <v>0.3572433873757371</v>
+      </c>
+      <c r="AA6">
+        <v>8.711626000000003</v>
+      </c>
+      <c r="AB6">
+        <v>0.04220933649737919</v>
+      </c>
+      <c r="AC6">
+        <v>24.28680820684258</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.55633435185</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>575.199137907774</v>
       </c>
-      <c r="V7">
-        <v>0.8633455734404059</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0.243741938</v>
+      </c>
+      <c r="Y7">
+        <v>0.261162948</v>
+      </c>
+      <c r="Z7">
+        <v>0.3572341217577718</v>
+      </c>
+      <c r="AA7">
+        <v>8.710504999999998</v>
+      </c>
+      <c r="AB7">
+        <v>0.04221343030454859</v>
+      </c>
+      <c r="AC7">
+        <v>24.28112871930625</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.55645009259</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>576.494121052689</v>
       </c>
-      <c r="V8">
-        <v>0.6992188593434691</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0.243747016</v>
+      </c>
+      <c r="Y8">
+        <v>0.261167404</v>
+      </c>
+      <c r="Z8">
+        <v>0.3572408441388015</v>
+      </c>
+      <c r="AA8">
+        <v>8.710194000000001</v>
+      </c>
+      <c r="AB8">
+        <v>0.04221560278307836</v>
+      </c>
+      <c r="AC8">
+        <v>24.33704682114021</v>
       </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.55656641204</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>576.1753942842728</v>
       </c>
-      <c r="V9">
-        <v>0.6747400253891528</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>0.243728606</v>
+      </c>
+      <c r="Y9">
+        <v>0.261152126</v>
+      </c>
+      <c r="Z9">
+        <v>0.3572171136676168</v>
+      </c>
+      <c r="AA9">
+        <v>8.711759999999998</v>
+      </c>
+      <c r="AB9">
+        <v>0.04220579367500808</v>
+      </c>
+      <c r="AC9">
+        <v>24.31793981177844</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.55668215278</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>576.2873340168155</v>
       </c>
-      <c r="V10">
-        <v>0.161698348182851</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.24369369</v>
+      </c>
+      <c r="Y10">
+        <v>0.26114067</v>
+      </c>
+      <c r="Z10">
+        <v>0.3571849157983368</v>
+      </c>
+      <c r="AA10">
+        <v>8.723489999999998</v>
+      </c>
+      <c r="AB10">
+        <v>0.04214864424059302</v>
+      </c>
+      <c r="AC10">
+        <v>24.28972982183456</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.55679847222</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>578.541176090229</v>
       </c>
-      <c r="V11">
-        <v>1.334744554150078</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.243682262</v>
+      </c>
+      <c r="Y11">
+        <v>0.261135894</v>
+      </c>
+      <c r="Z11">
+        <v>0.357173627173978</v>
+      </c>
+      <c r="AA11">
+        <v>8.726815999999999</v>
+      </c>
+      <c r="AB11">
+        <v>0.04213222818351833</v>
+      </c>
+      <c r="AC11">
+        <v>24.37522884459458</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.55691421296</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>577.4429470930698</v>
       </c>
-      <c r="V12">
-        <v>1.127042782690933</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
       </c>
+      <c r="X12">
+        <v>0.243690516</v>
+      </c>
+      <c r="Y12">
+        <v>0.261132394</v>
+      </c>
+      <c r="Z12">
+        <v>0.3571766996663101</v>
+      </c>
+      <c r="AA12">
+        <v>8.720939000000001</v>
+      </c>
+      <c r="AB12">
+        <v>0.0421593641839549</v>
+      </c>
+      <c r="AC12">
+        <v>24.34462750195294</v>
+      </c>
     </row>
-    <row r="13" spans="1:24">
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.55703053241</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>577.9642649970669</v>
       </c>
-      <c r="V13">
-        <v>0.5493489626572307</v>
-      </c>
-      <c r="W13" t="b">
+      <c r="V13" t="b">
         <v>1</v>
       </c>
+      <c r="X13">
+        <v>0.243669248</v>
+      </c>
+      <c r="Y13">
+        <v>0.261132076</v>
+      </c>
+      <c r="Z13">
+        <v>0.3571619570124389</v>
+      </c>
+      <c r="AA13">
+        <v>8.731414000000001</v>
+      </c>
+      <c r="AB13">
+        <v>0.0421099930280967</v>
+      </c>
+      <c r="AC13">
+        <v>24.33807116951552</v>
+      </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.55714627315</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>577.1414080438319</v>
       </c>
-      <c r="V14">
-        <v>0.4162915085858926</v>
-      </c>
-      <c r="W14" t="b">
+      <c r="V14" t="b">
         <v>1</v>
       </c>
+      <c r="X14">
+        <v>0.243677184</v>
+      </c>
+      <c r="Y14">
+        <v>0.261135576</v>
+      </c>
+      <c r="Z14">
+        <v>0.3571699302223266</v>
+      </c>
+      <c r="AA14">
+        <v>8.729196000000002</v>
+      </c>
+      <c r="AB14">
+        <v>0.04212097670655203</v>
+      </c>
+      <c r="AC14">
+        <v>24.30975980460088</v>
+      </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.55726259259</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>579.1663713483499</v>
       </c>
-      <c r="V15">
-        <v>1.018383492756991</v>
-      </c>
-      <c r="W15" t="b">
+      <c r="V15" t="b">
         <v>1</v>
       </c>
+      <c r="X15">
+        <v>0.243660044</v>
+      </c>
+      <c r="Y15">
+        <v>0.261133348</v>
+      </c>
+      <c r="Z15">
+        <v>0.357156607778396</v>
+      </c>
+      <c r="AA15">
+        <v>8.736651999999999</v>
+      </c>
+      <c r="AB15">
+        <v>0.04208557568763123</v>
+      </c>
+      <c r="AC15">
+        <v>24.37455015711172</v>
+      </c>
     </row>
-    <row r="16" spans="1:24">
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.55737833333</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>577.923512406952</v>
       </c>
-      <c r="V16">
-        <v>1.021180849773251</v>
-      </c>
-      <c r="W16" t="b">
+      <c r="V16" t="b">
         <v>1</v>
       </c>
+      <c r="X16">
+        <v>0.243642584</v>
+      </c>
+      <c r="Y16">
+        <v>0.261130802</v>
+      </c>
+      <c r="Z16">
+        <v>0.3571428348593322</v>
+      </c>
+      <c r="AA16">
+        <v>8.744109000000002</v>
+      </c>
+      <c r="AB16">
+        <v>0.04205018224138866</v>
+      </c>
+      <c r="AC16">
+        <v>24.30178901829577</v>
+      </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.55749465278</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>579.731093690927</v>
       </c>
-      <c r="V17">
-        <v>0.9247485938158517</v>
-      </c>
-      <c r="W17" t="b">
+      <c r="V17" t="b">
         <v>1</v>
       </c>
+      <c r="X17">
+        <v>0.243650202</v>
+      </c>
+      <c r="Y17">
+        <v>0.26113112</v>
+      </c>
+      <c r="Z17">
+        <v>0.357148264404428</v>
+      </c>
+      <c r="AA17">
+        <v>8.740459000000001</v>
+      </c>
+      <c r="AB17">
+        <v>0.04206735281278061</v>
+      </c>
+      <c r="AC17">
+        <v>24.3877524548354</v>
+      </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.55761097222</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>578.955427117128</v>
       </c>
-      <c r="V18">
-        <v>0.9068127977477624</v>
-      </c>
-      <c r="W18" t="b">
+      <c r="V18" t="b">
         <v>1</v>
       </c>
+      <c r="X18">
+        <v>0.243641632</v>
+      </c>
+      <c r="Y18">
+        <v>0.261132712</v>
+      </c>
+      <c r="Z18">
+        <v>0.3571435819388308</v>
+      </c>
+      <c r="AA18">
+        <v>8.745539999999998</v>
+      </c>
+      <c r="AB18">
+        <v>0.04204377385138768</v>
+      </c>
+      <c r="AC18">
+        <v>24.34147104774609</v>
+      </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.55772671296</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>578.0658483766354</v>
       </c>
-      <c r="V19">
-        <v>0.833271756992365</v>
-      </c>
-      <c r="W19" t="b">
+      <c r="V19" t="b">
         <v>1</v>
       </c>
+      <c r="X19">
+        <v>0.243653694</v>
+      </c>
+      <c r="Y19">
+        <v>0.261133348</v>
+      </c>
+      <c r="Z19">
+        <v>0.3571522756997843</v>
+      </c>
+      <c r="AA19">
+        <v>8.739826999999998</v>
+      </c>
+      <c r="AB19">
+        <v>0.0420706687359698</v>
+      </c>
+      <c r="AC19">
+        <v>24.31961681463077</v>
+      </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.55784303241</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>580.4951787875966</v>
       </c>
-      <c r="V20">
-        <v>1.22908040066946</v>
-      </c>
-      <c r="W20" t="b">
+      <c r="V20" t="b">
         <v>1</v>
       </c>
+      <c r="X20">
+        <v>0.24364925</v>
+      </c>
+      <c r="Y20">
+        <v>0.26113303</v>
+      </c>
+      <c r="Z20">
+        <v>0.3571490114539635</v>
+      </c>
+      <c r="AA20">
+        <v>8.741890000000005</v>
+      </c>
+      <c r="AB20">
+        <v>0.04206093877616594</v>
+      </c>
+      <c r="AC20">
+        <v>24.4161721748446</v>
+      </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.55795877315</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>578.7789976666811</v>
       </c>
-      <c r="V21">
-        <v>1.248699710051173</v>
-      </c>
-      <c r="W21" t="b">
+      <c r="V21" t="b">
         <v>1</v>
       </c>
+      <c r="X21">
+        <v>0.243639094</v>
+      </c>
+      <c r="Y21">
+        <v>0.261136532</v>
+      </c>
+      <c r="Z21">
+        <v>0.3571446436251394</v>
+      </c>
+      <c r="AA21">
+        <v>8.748719000000001</v>
+      </c>
+      <c r="AB21">
+        <v>0.04202947878761913</v>
+      </c>
+      <c r="AC21">
+        <v>24.32577960515124</v>
+      </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.55807509259</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>579.1643850926671</v>
       </c>
-      <c r="V22">
-        <v>0.9004455347537758</v>
-      </c>
-      <c r="W22" t="b">
+      <c r="V22" t="b">
         <v>1</v>
       </c>
+      <c r="X22">
+        <v>0.243656234</v>
+      </c>
+      <c r="Y22">
+        <v>0.261143852</v>
+      </c>
+      <c r="Z22">
+        <v>0.3571616886012002</v>
+      </c>
+      <c r="AA22">
+        <v>8.743808999999999</v>
+      </c>
+      <c r="AB22">
+        <v>0.04205363777783128</v>
+      </c>
+      <c r="AC22">
+        <v>24.35596926450741</v>
+      </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.55819141203</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>579.2191052462717</v>
       </c>
-      <c r="V23">
-        <v>0.2398653945175198</v>
-      </c>
-      <c r="W23" t="b">
+      <c r="V23" t="b">
         <v>1</v>
       </c>
+      <c r="X23">
+        <v>0.243671152</v>
+      </c>
+      <c r="Y23">
+        <v>0.261142896</v>
+      </c>
+      <c r="Z23">
+        <v>0.3571711668769946</v>
+      </c>
+      <c r="AA23">
+        <v>8.735871999999993</v>
+      </c>
+      <c r="AB23">
+        <v>0.0420907401038946</v>
+      </c>
+      <c r="AC23">
+        <v>24.3797608221312</v>
+      </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.55830773148</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>579.587678414489</v>
       </c>
-      <c r="V24">
-        <v>0.230223699847317</v>
-      </c>
-      <c r="W24" t="b">
+      <c r="V24" t="b">
         <v>1</v>
       </c>
+      <c r="X24">
+        <v>0.24366544</v>
+      </c>
+      <c r="Y24">
+        <v>0.261146398</v>
+      </c>
+      <c r="Z24">
+        <v>0.3571698305271149</v>
+      </c>
+      <c r="AA24">
+        <v>8.740479000000001</v>
+      </c>
+      <c r="AB24">
+        <v>0.04206965865466607</v>
+      </c>
+      <c r="AC24">
+        <v>24.38305579134792</v>
+      </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.55842347222</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>578.0084022414371</v>
       </c>
-      <c r="V25">
-        <v>0.8262123594054676</v>
-      </c>
-      <c r="W25" t="b">
+      <c r="V25" t="b">
         <v>1</v>
       </c>
+      <c r="X25">
+        <v>0.243684484</v>
+      </c>
+      <c r="Y25">
+        <v>0.26114067</v>
+      </c>
+      <c r="Z25">
+        <v>0.3571786349579089</v>
+      </c>
+      <c r="AA25">
+        <v>8.728093000000001</v>
+      </c>
+      <c r="AB25">
+        <v>0.04212696849329446</v>
+      </c>
+      <c r="AC25">
+        <v>24.34974175008449</v>
+      </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.55853921297</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>577.5525321595317</v>
       </c>
-      <c r="V26">
-        <v>1.068000549423038</v>
-      </c>
-      <c r="W26" t="b">
+      <c r="V26" t="b">
         <v>1</v>
       </c>
+      <c r="X26">
+        <v>0.243682262</v>
+      </c>
+      <c r="Y26">
+        <v>0.26113303</v>
+      </c>
+      <c r="Z26">
+        <v>0.3571715332587657</v>
+      </c>
+      <c r="AA26">
+        <v>8.725384000000005</v>
+      </c>
+      <c r="AB26">
+        <v>0.0421385202494242</v>
+      </c>
+      <c r="AC26">
+        <v>24.33720907151065</v>
+      </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.5586549537</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>576.4428586385635</v>
       </c>
-      <c r="V27">
-        <v>0.8052038693412922</v>
-      </c>
-      <c r="W27" t="b">
+      <c r="V27" t="b">
         <v>1</v>
       </c>
+      <c r="X27">
+        <v>0.243685754</v>
+      </c>
+      <c r="Y27">
+        <v>0.261128256</v>
+      </c>
+      <c r="Z27">
+        <v>0.3571704254052259</v>
+      </c>
+      <c r="AA27">
+        <v>8.721250999999995</v>
+      </c>
+      <c r="AB27">
+        <v>0.04215724191376893</v>
+      </c>
+      <c r="AC27">
+        <v>24.30124104109043</v>
+      </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.55877127315</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>578.4574023116396</v>
       </c>
-      <c r="V28">
-        <v>1.009005411782983</v>
-      </c>
-      <c r="W28" t="b">
+      <c r="V28" t="b">
         <v>1</v>
       </c>
+      <c r="X28">
+        <v>0.243678454</v>
+      </c>
+      <c r="Y28">
+        <v>0.261132076</v>
+      </c>
+      <c r="Z28">
+        <v>0.3571682377534429</v>
+      </c>
+      <c r="AA28">
+        <v>8.726810999999998</v>
+      </c>
+      <c r="AB28">
+        <v>0.04213165104023298</v>
+      </c>
+      <c r="AC28">
+        <v>24.37136541583366</v>
+      </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.55888701389</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>580.3304704557553</v>
       </c>
-      <c r="V29">
-        <v>1.944234901977101</v>
-      </c>
-      <c r="W29" t="b">
+      <c r="V29" t="b">
         <v>1</v>
       </c>
+      <c r="X29">
+        <v>0.243652108</v>
+      </c>
+      <c r="Y29">
+        <v>0.26114067</v>
+      </c>
+      <c r="Z29">
+        <v>0.3571565472742905</v>
+      </c>
+      <c r="AA29">
+        <v>8.744281000000001</v>
+      </c>
+      <c r="AB29">
+        <v>0.04205092506203646</v>
+      </c>
+      <c r="AC29">
+        <v>24.40343312435133</v>
+      </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.55900333334</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>579.242370170062</v>
       </c>
-      <c r="V30">
-        <v>0.9406133675225098</v>
-      </c>
-      <c r="W30" t="b">
+      <c r="V30" t="b">
         <v>1</v>
       </c>
+      <c r="X30">
+        <v>0.243650838</v>
+      </c>
+      <c r="Y30">
+        <v>0.26113685</v>
+      </c>
+      <c r="Z30">
+        <v>0.3571528878310026</v>
+      </c>
+      <c r="AA30">
+        <v>8.743006000000001</v>
+      </c>
+      <c r="AB30">
+        <v>0.04205630405971276</v>
+      </c>
+      <c r="AC30">
+        <v>24.36079324414082</v>
+      </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.55911965277</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>578.5958938466331</v>
       </c>
-      <c r="V31">
-        <v>0.8766080349261535</v>
-      </c>
-      <c r="W31" t="b">
+      <c r="V31" t="b">
         <v>1</v>
       </c>
+      <c r="X31">
+        <v>0.243656234</v>
+      </c>
+      <c r="Y31">
+        <v>0.261130802</v>
+      </c>
+      <c r="Z31">
+        <v>0.3571521470189224</v>
+      </c>
+      <c r="AA31">
+        <v>8.737284000000002</v>
+      </c>
+      <c r="AB31">
+        <v>0.0420822074422861</v>
+      </c>
+      <c r="AC31">
+        <v>24.34859243010896</v>
+      </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.55923539352</v>
       </c>
@@ -2689,11 +3190,26 @@
       <c r="U32">
         <v>577.1025561595735</v>
       </c>
-      <c r="V32">
-        <v>1.097481441287503</v>
-      </c>
-      <c r="W32" t="b">
+      <c r="V32" t="b">
         <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.243708608</v>
+      </c>
+      <c r="Y32">
+        <v>0.26113876</v>
+      </c>
+      <c r="Z32">
+        <v>0.3571936975754685</v>
+      </c>
+      <c r="AA32">
+        <v>8.715076000000003</v>
+      </c>
+      <c r="AB32">
+        <v>0.0421880261803861</v>
+      </c>
+      <c r="AC32">
+        <v>24.34681774802782</v>
       </c>
     </row>
   </sheetData>
